--- a/data/trans_dic/IP16A02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A02-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,27; 50,95</t>
+          <t>9,78; 50,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,32; 58,28</t>
+          <t>19,06; 56,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,82; 57,22</t>
+          <t>21,61; 57,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 38,5</t>
+          <t>8,65; 39,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,9; 74,92</t>
+          <t>27,47; 75,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,5; 58,79</t>
+          <t>26,62; 60,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,14; 55,66</t>
+          <t>23,55; 56,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,06; 49,22</t>
+          <t>12,37; 46,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,03; 55,71</t>
+          <t>22,76; 55,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,56; 52,12</t>
+          <t>27,17; 52,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,12; 50,57</t>
+          <t>28,03; 51,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,35; 37,77</t>
+          <t>13,51; 36,91</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,29; 36,92</t>
+          <t>7,31; 36,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,97; 58,35</t>
+          <t>30,06; 56,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,5; 47,32</t>
+          <t>21,0; 47,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,93; 74,58</t>
+          <t>11,27; 73,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,63; 43,45</t>
+          <t>12,77; 43,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,77; 59,92</t>
+          <t>34,03; 59,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,0; 63,46</t>
+          <t>30,24; 62,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,29; 72,24</t>
+          <t>47,07; 71,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,45; 34,17</t>
+          <t>12,54; 34,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35,95; 54,85</t>
+          <t>35,38; 55,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,8; 50,68</t>
+          <t>28,69; 50,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,38; 67,1</t>
+          <t>17,49; 67,08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 44,89</t>
+          <t>5,89; 45,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,95; 72,35</t>
+          <t>38,78; 74,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,31; 64,55</t>
+          <t>14,1; 60,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,33; 51,49</t>
+          <t>17,67; 51,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,02; 70,29</t>
+          <t>23,25; 65,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,34; 56,63</t>
+          <t>24,72; 57,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,45; 61,87</t>
+          <t>8,03; 62,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 29,23</t>
+          <t>3,02; 28,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,97; 48,12</t>
+          <t>16,92; 46,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35,73; 60,62</t>
+          <t>36,19; 61,7</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,6; 54,79</t>
+          <t>17,84; 53,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,58; 34,44</t>
+          <t>12,82; 34,47</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,29; 64,95</t>
+          <t>24,81; 65,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,9; 54,33</t>
+          <t>24,57; 55,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,51; 59,13</t>
+          <t>31,78; 59,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,51; 73,08</t>
+          <t>25,3; 73,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,88; 63,3</t>
+          <t>22,97; 63,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,51; 57,05</t>
+          <t>14,1; 55,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,19; 51,25</t>
+          <t>21,17; 51,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,41; 88,52</t>
+          <t>34,63; 88,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,89; 57,59</t>
+          <t>29,53; 58,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,81; 50,41</t>
+          <t>25,15; 50,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,22; 50,38</t>
+          <t>29,87; 50,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,76; 77,0</t>
+          <t>39,0; 76,65</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,86</t>
+          <t>0,0; 44,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,34; 77,98</t>
+          <t>41,33; 78,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,51; 65,03</t>
+          <t>8,37; 63,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,77; 79,28</t>
+          <t>28,94; 79,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,33; 62,81</t>
+          <t>8,6; 62,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,76; 65,52</t>
+          <t>21,61; 66,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,8; 72,24</t>
+          <t>9,16; 65,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,34; 67,37</t>
+          <t>15,02; 66,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,11; 44,48</t>
+          <t>9,4; 41,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39,94; 69,21</t>
+          <t>39,6; 67,68</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,39; 55,98</t>
+          <t>17,54; 58,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,28; 65,79</t>
+          <t>26,07; 64,55</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,18; 65,76</t>
+          <t>18,26; 66,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,18; 58,13</t>
+          <t>15,96; 58,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,29</t>
+          <t>0,0; 36,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,01; 57,44</t>
+          <t>6,86; 55,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,3; 65,99</t>
+          <t>21,96; 70,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,52; 59,26</t>
+          <t>21,68; 59,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,37</t>
+          <t>0,0; 40,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,33; 59,18</t>
+          <t>20,82; 61,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,42; 56,84</t>
+          <t>24,03; 57,44</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,3; 51,91</t>
+          <t>24,1; 52,5</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,5; 28,22</t>
+          <t>3,54; 28,74</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,28; 49,62</t>
+          <t>19,31; 51,18</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,0; 67,07</t>
+          <t>32,68; 68,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27,88; 55,38</t>
+          <t>26,94; 56,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,88; 67,69</t>
+          <t>30,62; 67,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43,35; 72,48</t>
+          <t>44,65; 73,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,05; 56,02</t>
+          <t>24,64; 56,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,63; 39,89</t>
+          <t>12,63; 40,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,47; 71,04</t>
+          <t>24,7; 70,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28,85; 59,39</t>
+          <t>29,47; 58,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,26; 55,61</t>
+          <t>32,78; 57,13</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23,75; 44,32</t>
+          <t>23,18; 42,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34,5; 62,43</t>
+          <t>36,7; 61,68</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,83; 61,5</t>
+          <t>38,63; 61,19</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,73; 50,33</t>
+          <t>21,72; 51,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,61; 43,74</t>
+          <t>13,36; 42,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26,73; 55,04</t>
+          <t>26,19; 52,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18,39; 71,5</t>
+          <t>18,47; 70,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,86; 59,38</t>
+          <t>34,52; 60,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,13; 55,96</t>
+          <t>23,6; 55,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,75; 49,27</t>
+          <t>21,55; 49,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,8; 77,71</t>
+          <t>26,65; 76,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33,45; 52,77</t>
+          <t>33,09; 51,77</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22,49; 45,06</t>
+          <t>22,61; 44,72</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28,85; 48,32</t>
+          <t>28,06; 47,82</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,26; 67,48</t>
+          <t>30,06; 64,61</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26,2; 40,04</t>
+          <t>25,9; 39,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35,18; 47,32</t>
+          <t>36,17; 47,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33,13; 45,07</t>
+          <t>32,81; 45,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24,21; 50,31</t>
+          <t>24,32; 50,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34,93; 47,9</t>
+          <t>34,86; 47,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,35; 45,05</t>
+          <t>33,53; 44,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,62; 44,17</t>
+          <t>30,69; 43,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>37,44; 50,87</t>
+          <t>37,46; 50,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33,06; 42,15</t>
+          <t>32,53; 42,16</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36,21; 44,92</t>
+          <t>36,28; 44,98</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33,52; 42,23</t>
+          <t>33,53; 42,68</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>33,13; 48,3</t>
+          <t>32,5; 47,98</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3115</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6706</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7409</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6536</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>6211</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10977</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9391</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>6142</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>9326</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17683</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16800</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>12678</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1141; 5914</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3633; 10752</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4225; 11326</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2627; 11956</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3333; 9144</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6872; 15669</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5769; 13735</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2760; 10409</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5419; 13144</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>12192; 23559</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>12347; 22732</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>7121; 19455</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3083</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14681</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10300</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25331</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5062</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>10728</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>28872</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>8145</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>32112</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>54203</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1222; 6184</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>10096; 19145</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6388; 14477</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>7108; 46588</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2536; 8542</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>12691; 22063</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7051; 14607</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>22668; 34556</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4588; 12590</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>25077; 39582</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>15418; 26879</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>19457; 74608</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2236</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3679</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5910</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4370</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>9694</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2835</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2441</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6606</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20694</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6514</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>8351</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>684; 5316</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7476; 14412</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1450; 6273</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3169; 9236</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2455; 6909</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5848; 13591</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>722; 5603</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>613; 5826</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3754; 10364</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>15538; 26491</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3438; 10387</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4901; 13175</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7078</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9593</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15721</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6355</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6952</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5731</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>10231</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7554</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>14030</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>15325</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>25953</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>13909</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4057; 10750</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6115; 13808</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>11094; 20692</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3168; 9179</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3774; 10367</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2361; 9337</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>6270; 15256</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3835; 9767</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>9680; 19016</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>10472; 21207</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>19275; 32870</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>9201; 18085</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1311</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12179</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2584</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4450</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5912</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2663</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>4207</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3978</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>18091</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5247</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>8656</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4019</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8188; 15519</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>651; 4934</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2384; 6583</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>672; 4896</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2936; 8990</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>665; 4759</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1606; 7126</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1593; 6984</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>13227; 22607</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2637; 8733</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>4935; 12216</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>4857</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4467</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1475</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4481</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>7843</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>5247</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>9338</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>12310</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2265</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>7216</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2260; 8228</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2098; 7657</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3835</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>527; 4242</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2356; 7528</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>4230; 11536</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3832</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2833; 8426</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>5553; 13272</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>7869; 17143</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>710; 5764</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>4110; 10894</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>10598</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>13735</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>9978</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>17633</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>10685</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>6695</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>19437</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>21283</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>20939</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>16673</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>37070</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>7025; 14672</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>9029; 18854</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>6036; 13345</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>13300; 21878</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>6537; 14961</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3686; 11739</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3450; 9813</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>13069; 25741</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>15742; 27438</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>14533; 26671</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>12361; 20771</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>28643; 45369</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>9017</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6349</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>12026</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3335</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>18915</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>10407</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>10819</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>27932</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>16756</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>22845</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>9531</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>5631; 13264</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>3252; 10354</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>7861; 15903</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1498; 5713</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>13760; 23958</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>6348; 15025</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>6523; 14910</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>3119; 8919</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>21772; 34061</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>11587; 22919</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>16914; 28829</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>5958; 12805</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>41295</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>78711</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>63172</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>71517</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>59343</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>75199</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>54153</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>80096</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>100638</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>153910</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>117324</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>151613</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>32457; 49838</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>67876; 89891</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>53571; 73725</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>43225; 89984</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>50167; 68950</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>64620; 86300</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>45230; 63813</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>68245; 92357</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>87583; 113508</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>138008; 171072</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>104160; 132584</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>116988; 172684</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A02-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,78; 50,69</t>
+          <t>9,75; 50,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,06; 56,41</t>
+          <t>19,93; 57,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,61; 57,92</t>
+          <t>20,58; 55,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,65; 39,35</t>
+          <t>8,98; 39,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,47; 75,35</t>
+          <t>25,08; 70,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,62; 60,7</t>
+          <t>26,88; 59,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,55; 56,06</t>
+          <t>22,85; 53,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,37; 46,63</t>
+          <t>11,82; 48,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,76; 55,22</t>
+          <t>24,97; 55,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,17; 52,5</t>
+          <t>27,35; 53,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,03; 51,6</t>
+          <t>26,77; 50,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,51; 36,91</t>
+          <t>14,29; 39,28</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 36,97</t>
+          <t>7,27; 36,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,06; 56,99</t>
+          <t>29,91; 58,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,0; 47,6</t>
+          <t>20,93; 47,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,27; 73,89</t>
+          <t>14,64; 74,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,77; 43,02</t>
+          <t>12,3; 42,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,03; 59,16</t>
+          <t>33,37; 58,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,24; 62,64</t>
+          <t>31,2; 64,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,07; 71,75</t>
+          <t>47,9; 71,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,54; 34,41</t>
+          <t>13,48; 34,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35,38; 55,84</t>
+          <t>35,52; 54,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,69; 50,02</t>
+          <t>29,55; 50,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,49; 67,08</t>
+          <t>23,96; 67,61</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,89; 45,72</t>
+          <t>5,8; 45,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,78; 74,77</t>
+          <t>38,8; 74,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,1; 60,98</t>
+          <t>14,48; 63,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,67; 51,48</t>
+          <t>18,59; 52,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,25; 65,42</t>
+          <t>23,13; 64,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,72; 57,45</t>
+          <t>26,04; 58,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,03; 62,35</t>
+          <t>8,11; 62,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 28,72</t>
+          <t>3,71; 29,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,92; 46,71</t>
+          <t>14,72; 47,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,19; 61,7</t>
+          <t>35,89; 61,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,84; 53,89</t>
+          <t>17,84; 52,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,82; 34,47</t>
+          <t>12,74; 34,07</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,81; 65,75</t>
+          <t>23,07; 64,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,57; 55,47</t>
+          <t>23,09; 55,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,78; 59,26</t>
+          <t>32,07; 58,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,3; 73,31</t>
+          <t>23,69; 74,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,97; 63,11</t>
+          <t>23,4; 63,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,1; 55,74</t>
+          <t>16,9; 57,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,17; 51,52</t>
+          <t>21,06; 50,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,63; 88,2</t>
+          <t>36,65; 87,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,53; 58,02</t>
+          <t>29,43; 57,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,15; 50,93</t>
+          <t>24,04; 51,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,87; 50,94</t>
+          <t>31,11; 51,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,0; 76,65</t>
+          <t>39,2; 76,18</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,04</t>
+          <t>0,0; 45,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,33; 78,33</t>
+          <t>44,81; 80,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,37; 63,43</t>
+          <t>7,9; 62,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,94; 79,92</t>
+          <t>29,07; 79,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,6; 62,61</t>
+          <t>8,23; 62,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,61; 66,17</t>
+          <t>21,49; 65,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,16; 65,53</t>
+          <t>10,22; 67,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,02; 66,67</t>
+          <t>16,17; 68,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,4; 41,21</t>
+          <t>7,93; 44,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39,6; 67,68</t>
+          <t>39,34; 68,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,54; 58,07</t>
+          <t>16,92; 58,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,07; 64,55</t>
+          <t>26,84; 64,05</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,26; 66,47</t>
+          <t>20,89; 66,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,96; 58,26</t>
+          <t>16,13; 59,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,25</t>
+          <t>0,0; 36,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,86; 55,24</t>
+          <t>7,11; 57,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,96; 70,17</t>
+          <t>18,31; 65,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,68; 59,13</t>
+          <t>21,73; 59,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,44</t>
+          <t>0,0; 45,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,82; 61,92</t>
+          <t>20,16; 60,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24,03; 57,44</t>
+          <t>25,23; 57,37</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,1; 52,5</t>
+          <t>24,85; 53,24</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,54; 28,74</t>
+          <t>3,61; 30,45</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,31; 51,18</t>
+          <t>19,35; 50,16</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32,68; 68,24</t>
+          <t>32,49; 68,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,94; 56,26</t>
+          <t>27,34; 54,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30,62; 67,7</t>
+          <t>32,08; 68,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44,65; 73,45</t>
+          <t>42,6; 72,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,64; 56,4</t>
+          <t>24,51; 54,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,63; 40,21</t>
+          <t>13,36; 40,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,7; 70,27</t>
+          <t>28,57; 68,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,47; 58,04</t>
+          <t>29,14; 59,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>32,78; 57,13</t>
+          <t>33,64; 56,15</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23,18; 42,54</t>
+          <t>24,24; 43,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36,7; 61,68</t>
+          <t>36,63; 63,81</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,63; 61,19</t>
+          <t>38,55; 60,68</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,72; 51,16</t>
+          <t>22,25; 51,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,36; 42,52</t>
+          <t>13,9; 43,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26,19; 52,98</t>
+          <t>26,68; 54,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18,47; 70,41</t>
+          <t>18,8; 68,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,52; 60,09</t>
+          <t>34,82; 60,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,6; 55,85</t>
+          <t>24,22; 54,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,55; 49,26</t>
+          <t>23,03; 49,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>26,65; 76,19</t>
+          <t>29,71; 78,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33,09; 51,77</t>
+          <t>33,49; 52,63</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22,61; 44,72</t>
+          <t>22,56; 43,55</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28,06; 47,82</t>
+          <t>28,29; 48,4</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,06; 64,61</t>
+          <t>30,7; 66,98</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25,9; 39,77</t>
+          <t>26,9; 40,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36,17; 47,91</t>
+          <t>35,84; 48,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32,81; 45,16</t>
+          <t>32,48; 44,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24,32; 50,63</t>
+          <t>24,68; 50,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34,86; 47,91</t>
+          <t>35,37; 47,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,53; 44,78</t>
+          <t>33,24; 45,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,69; 43,3</t>
+          <t>30,42; 43,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>37,46; 50,69</t>
+          <t>36,84; 50,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32,53; 42,16</t>
+          <t>33,17; 42,56</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36,28; 44,98</t>
+          <t>36,45; 45,44</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33,53; 42,68</t>
+          <t>33,28; 42,48</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>32,5; 47,98</t>
+          <t>31,55; 47,77</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1141; 5914</t>
+          <t>1137; 5936</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3633; 10752</t>
+          <t>3798; 10938</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4225; 11326</t>
+          <t>4024; 10825</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2627; 11956</t>
+          <t>2728; 11853</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3333; 9144</t>
+          <t>3044; 8581</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6872; 15669</t>
+          <t>6938; 15484</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5769; 13735</t>
+          <t>5599; 13078</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2760; 10409</t>
+          <t>2639; 10878</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5419; 13144</t>
+          <t>5943; 13220</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12192; 23559</t>
+          <t>12273; 23979</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12347; 22732</t>
+          <t>11792; 22322</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7121; 19455</t>
+          <t>7534; 20702</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1222; 6184</t>
+          <t>1216; 6143</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10096; 19145</t>
+          <t>10046; 19551</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6388; 14477</t>
+          <t>6366; 14580</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7108; 46588</t>
+          <t>9231; 47154</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2536; 8542</t>
+          <t>2441; 8514</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12691; 22063</t>
+          <t>12446; 21939</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7051; 14607</t>
+          <t>7276; 15001</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22668; 34556</t>
+          <t>23071; 34663</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4588; 12590</t>
+          <t>4933; 12742</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25077; 39582</t>
+          <t>25181; 38856</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15418; 26879</t>
+          <t>15876; 27018</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19457; 74608</t>
+          <t>26651; 75190</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>684; 5316</t>
+          <t>674; 5307</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7476; 14412</t>
+          <t>7480; 14431</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1450; 6273</t>
+          <t>1489; 6550</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3169; 9236</t>
+          <t>3335; 9411</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2455; 6909</t>
+          <t>2443; 6815</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5848; 13591</t>
+          <t>6161; 13902</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>722; 5603</t>
+          <t>729; 5600</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>613; 5826</t>
+          <t>753; 6078</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3754; 10364</t>
+          <t>3266; 10642</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15538; 26491</t>
+          <t>15411; 26535</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3438; 10387</t>
+          <t>3438; 10117</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4901; 13175</t>
+          <t>4872; 13022</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4057; 10750</t>
+          <t>3772; 10583</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6115; 13808</t>
+          <t>5749; 13862</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11094; 20692</t>
+          <t>11199; 20346</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3168; 9179</t>
+          <t>2966; 9320</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3774; 10367</t>
+          <t>3844; 10482</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2361; 9337</t>
+          <t>2831; 9572</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6270; 15256</t>
+          <t>6236; 15032</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3835; 9767</t>
+          <t>4058; 9686</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9680; 19016</t>
+          <t>9648; 18737</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10472; 21207</t>
+          <t>10009; 21323</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19275; 32870</t>
+          <t>20073; 33174</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9201; 18085</t>
+          <t>9249; 17974</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4019</t>
+          <t>0; 4186</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8188; 15519</t>
+          <t>8878; 15860</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>651; 4934</t>
+          <t>615; 4827</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2384; 6583</t>
+          <t>2395; 6549</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>672; 4896</t>
+          <t>643; 4900</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2936; 8990</t>
+          <t>2920; 8946</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>665; 4759</t>
+          <t>742; 4866</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1606; 7126</t>
+          <t>1728; 7327</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1593; 6984</t>
+          <t>1345; 7474</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13227; 22607</t>
+          <t>13139; 22963</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2637; 8733</t>
+          <t>2544; 8818</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4935; 12216</t>
+          <t>5079; 12122</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2260; 8228</t>
+          <t>2586; 8170</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2098; 7657</t>
+          <t>2120; 7849</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3835</t>
+          <t>0; 3817</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>527; 4242</t>
+          <t>546; 4426</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2356; 7528</t>
+          <t>1965; 7058</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4230; 11536</t>
+          <t>4239; 11551</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3832</t>
+          <t>0; 4343</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2833; 8426</t>
+          <t>2743; 8238</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5553; 13272</t>
+          <t>5830; 13258</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7869; 17143</t>
+          <t>8114; 17386</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>710; 5764</t>
+          <t>724; 6108</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4110; 10894</t>
+          <t>4119; 10677</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7025; 14672</t>
+          <t>6986; 14732</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9029; 18854</t>
+          <t>9161; 18366</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6036; 13345</t>
+          <t>6323; 13457</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13300; 21878</t>
+          <t>12688; 21726</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6537; 14961</t>
+          <t>6502; 14353</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3686; 11739</t>
+          <t>3900; 11746</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3450; 9813</t>
+          <t>3989; 9514</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13069; 25741</t>
+          <t>12923; 26309</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15742; 27438</t>
+          <t>16154; 26966</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14533; 26671</t>
+          <t>15197; 27555</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12361; 20771</t>
+          <t>12334; 21490</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28643; 45369</t>
+          <t>28579; 44986</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5631; 13264</t>
+          <t>5767; 13450</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3252; 10354</t>
+          <t>3385; 10619</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7861; 15903</t>
+          <t>8010; 16352</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1498; 5713</t>
+          <t>1526; 5560</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13760; 23958</t>
+          <t>13881; 23921</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6348; 15025</t>
+          <t>6516; 14668</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6523; 14910</t>
+          <t>6971; 15071</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3119; 8919</t>
+          <t>3479; 9134</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>21772; 34061</t>
+          <t>22035; 34628</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11587; 22919</t>
+          <t>11564; 22320</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>16914; 28829</t>
+          <t>17054; 29181</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5958; 12805</t>
+          <t>6084; 13275</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>32457; 49838</t>
+          <t>33713; 51225</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>67876; 89891</t>
+          <t>67251; 90680</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53571; 73725</t>
+          <t>53029; 73357</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>43225; 89984</t>
+          <t>43856; 89860</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>50167; 68950</t>
+          <t>50907; 68801</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>64620; 86300</t>
+          <t>64064; 87054</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45230; 63813</t>
+          <t>44835; 63534</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>68245; 92357</t>
+          <t>67131; 91778</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>87583; 113508</t>
+          <t>89310; 114590</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>138008; 171072</t>
+          <t>138640; 172841</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>104160; 132584</t>
+          <t>103391; 131952</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>116988; 172684</t>
+          <t>113536; 171925</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A02-Provincia-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>51,18%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>42,52%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38,33%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24,96%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>26,7%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>35,18%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>37,89%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21,51%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>51,18%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38,33%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,75; 50,88</t>
+          <t>27,9; 74,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,93; 57,39</t>
+          <t>24,5; 58,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,58; 55,36</t>
+          <t>23,14; 55,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,98; 39,01</t>
+          <t>11,18; 46,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,08; 70,71</t>
+          <t>10,27; 50,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,88; 59,98</t>
+          <t>18,32; 58,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,85; 53,38</t>
+          <t>21,82; 57,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,82; 48,73</t>
+          <t>13,88; 44,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,97; 55,54</t>
+          <t>23,03; 55,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,35; 53,44</t>
+          <t>28,56; 52,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,77; 50,67</t>
+          <t>27,12; 50,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,29; 39,28</t>
+          <t>16,13; 39,33</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>25,49%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>46,74%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>46,01%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>59,33%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>18,43%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>43,7%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>33,87%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>40,17%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>25,49%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>46,74%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>46,01%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>61,69%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,27; 36,72</t>
+          <t>12,63; 43,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,91; 58,2</t>
+          <t>33,77; 59,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,93; 47,94</t>
+          <t>30,0; 63,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,64; 74,78</t>
+          <t>45,43; 72,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,3; 42,88</t>
+          <t>7,29; 36,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,37; 58,83</t>
+          <t>30,97; 58,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,2; 64,33</t>
+          <t>21,5; 47,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,9; 71,97</t>
+          <t>47,82; 78,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,48; 34,83</t>
+          <t>13,45; 34,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35,52; 54,81</t>
+          <t>35,95; 54,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,55; 50,28</t>
+          <t>28,8; 50,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,96; 67,61</t>
+          <t>51,98; 71,59</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>41,38%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40,98%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>31,55%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>19,23%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>57,07%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>35,76%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>32,94%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>41,38%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>40,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>31,55%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,8; 45,65</t>
+          <t>18,02; 70,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,8; 74,87</t>
+          <t>24,34; 56,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,48; 63,68</t>
+          <t>8,45; 61,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,59; 52,46</t>
+          <t>3,31; 28,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,13; 64,53</t>
+          <t>5,95; 44,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,04; 58,76</t>
+          <t>37,95; 72,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,11; 62,31</t>
+          <t>14,31; 64,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 29,96</t>
+          <t>17,77; 51,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,72; 47,96</t>
+          <t>14,97; 48,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35,89; 61,8</t>
+          <t>35,73; 60,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,84; 52,49</t>
+          <t>18,6; 54,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,74; 34,07</t>
+          <t>13,08; 35,51</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>42,32%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34,22%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34,55%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>70,23%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>43,29%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>38,54%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>45,03%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>50,76%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>42,32%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>34,22%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,55%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,36%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,07; 64,72</t>
+          <t>22,88; 63,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,09; 55,69</t>
+          <t>16,51; 57,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,07; 58,27</t>
+          <t>20,19; 51,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,69; 74,43</t>
+          <t>43,27; 89,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,4; 63,82</t>
+          <t>23,29; 64,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,9; 57,15</t>
+          <t>22,9; 54,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,06; 50,76</t>
+          <t>31,51; 59,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,65; 87,47</t>
+          <t>22,67; 70,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,43; 57,16</t>
+          <t>28,89; 57,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,04; 51,21</t>
+          <t>23,81; 50,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,11; 51,41</t>
+          <t>30,22; 50,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,2; 76,18</t>
+          <t>38,57; 76,87</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>34,11%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43,51%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>36,68%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>44,76%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>14,36%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>61,47%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>33,22%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>54,02%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>34,11%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>43,51%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>36,68%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>49,22%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,87</t>
+          <t>8,33; 62,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44,81; 80,05</t>
+          <t>20,76; 65,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,9; 62,06</t>
+          <t>10,8; 72,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,07; 79,5</t>
+          <t>19,33; 72,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,23; 62,66</t>
+          <t>0,0; 44,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,49; 65,84</t>
+          <t>41,34; 77,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,22; 67,01</t>
+          <t>8,51; 65,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,17; 68,54</t>
+          <t>30,06; 79,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,93; 44,1</t>
+          <t>11,11; 44,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39,34; 68,75</t>
+          <t>39,94; 69,21</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,92; 58,63</t>
+          <t>17,39; 55,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,84; 64,05</t>
+          <t>29,26; 68,24</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>41,77%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>40,2%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38,25%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>39,23%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>33,99%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>13,94%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25,63%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>41,77%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>40,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,89; 66,0</t>
+          <t>18,3; 65,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,13; 59,72</t>
+          <t>22,52; 59,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,08</t>
+          <t>0,0; 36,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,11; 57,64</t>
+          <t>18,17; 59,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,31; 65,78</t>
+          <t>17,18; 65,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,73; 59,2</t>
+          <t>16,18; 58,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,84</t>
+          <t>0,0; 36,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,16; 60,55</t>
+          <t>7,93; 57,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,23; 57,37</t>
+          <t>25,42; 56,84</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,85; 53,24</t>
+          <t>24,3; 51,91</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,61; 30,45</t>
+          <t>3,5; 28,22</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,35; 50,16</t>
+          <t>18,92; 49,45</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>40,28%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>24,68%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>47,94%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>43,11%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>49,3%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>40,99%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>50,62%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>59,2%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>40,28%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>47,94%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,5%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32,49; 68,52</t>
+          <t>27,05; 56,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27,34; 54,81</t>
+          <t>13,63; 39,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,08; 68,27</t>
+          <t>28,47; 71,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42,6; 72,94</t>
+          <t>28,25; 59,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,51; 54,11</t>
+          <t>33,0; 67,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,36; 40,24</t>
+          <t>27,88; 55,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,57; 68,13</t>
+          <t>32,88; 67,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,14; 59,32</t>
+          <t>42,74; 72,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,64; 56,15</t>
+          <t>33,26; 55,61</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24,24; 43,95</t>
+          <t>23,75; 44,32</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36,63; 63,81</t>
+          <t>34,5; 62,43</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,55; 60,68</t>
+          <t>36,43; 60,3</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>47,45%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>38,68%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>35,74%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>52,15%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>34,78%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>26,08%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>40,06%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>41,11%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>47,45%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>38,68%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>35,74%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,71%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,25; 51,88</t>
+          <t>35,86; 59,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,9; 43,61</t>
+          <t>24,13; 55,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26,68; 54,47</t>
+          <t>22,75; 49,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18,8; 68,53</t>
+          <t>29,1; 77,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,82; 60,0</t>
+          <t>21,73; 50,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,22; 54,52</t>
+          <t>13,61; 43,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,03; 49,79</t>
+          <t>26,73; 55,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,71; 78,02</t>
+          <t>17,35; 72,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33,49; 52,63</t>
+          <t>33,45; 52,77</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22,56; 43,55</t>
+          <t>22,49; 45,06</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28,29; 48,4</t>
+          <t>28,85; 48,32</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,7; 66,98</t>
+          <t>30,45; 68,65</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>41,23%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>39,02%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>36,74%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>43,98%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>32,96%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>41,95%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>38,69%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>40,24%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>41,23%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>39,02%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>36,74%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26,9; 40,88</t>
+          <t>34,93; 47,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35,84; 48,33</t>
+          <t>33,35; 45,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32,48; 44,93</t>
+          <t>30,62; 44,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24,68; 50,56</t>
+          <t>37,41; 51,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35,37; 47,81</t>
+          <t>26,2; 40,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,24; 45,17</t>
+          <t>35,18; 47,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,42; 43,11</t>
+          <t>33,13; 45,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36,84; 50,37</t>
+          <t>42,06; 55,95</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33,17; 42,56</t>
+          <t>33,06; 42,15</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36,45; 45,44</t>
+          <t>36,21; 44,92</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33,28; 42,48</t>
+          <t>33,52; 42,23</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>31,55; 47,77</t>
+          <t>41,64; 50,97</t>
         </is>
       </c>
     </row>
@@ -1951,13 +1951,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6211</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10977</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9391</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4811</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3115</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>6706</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>7409</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6536</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>6211</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10977</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9391</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12678</t>
+          <t>10517</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1137; 5936</t>
+          <t>3386; 9092</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3798; 10938</t>
+          <t>6326; 15175</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4024; 10825</t>
+          <t>5670; 13636</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2728; 11853</t>
+          <t>2155; 8908</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3044; 8581</t>
+          <t>1199; 5945</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6938; 15484</t>
+          <t>3491; 11108</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5599; 13078</t>
+          <t>4266; 11189</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2639; 10878</t>
+          <t>2887; 9293</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5943; 13220</t>
+          <t>5483; 13260</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12273; 23979</t>
+          <t>12818; 23390</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11792; 22322</t>
+          <t>11948; 22281</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7534; 20702</t>
+          <t>6465; 15759</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5062</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10728</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25314</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3083</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>14681</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10300</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>25331</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5062</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17431</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10728</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28872</t>
+          <t>24922</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54203</t>
+          <t>50236</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1216; 6143</t>
+          <t>2508; 8628</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10046; 19551</t>
+          <t>12596; 22346</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6366; 14580</t>
+          <t>6995; 14798</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9231; 47154</t>
+          <t>19385; 30775</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2441; 8514</t>
+          <t>1219; 6177</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12446; 21939</t>
+          <t>10403; 19600</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7276; 15001</t>
+          <t>6538; 14392</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23071; 34663</t>
+          <t>18540; 30335</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4933; 12742</t>
+          <t>4921; 12502</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25181; 38856</t>
+          <t>25483; 38878</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15876; 27018</t>
+          <t>15476; 27233</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26651; 75190</t>
+          <t>42327; 58300</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4370</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9694</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2835</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2141</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2236</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>11000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3679</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5910</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4370</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9694</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2835</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>7873</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>674; 5307</t>
+          <t>1904; 7424</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7480; 14431</t>
+          <t>5758; 13398</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1489; 6550</t>
+          <t>760; 5560</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3335; 9411</t>
+          <t>585; 5031</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2443; 6815</t>
+          <t>691; 5220</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6161; 13902</t>
+          <t>7315; 13946</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>729; 5600</t>
+          <t>1472; 6640</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>753; 6078</t>
+          <t>3057; 8921</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3266; 10642</t>
+          <t>3323; 10677</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15411; 26535</t>
+          <t>15340; 26027</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3438; 10117</t>
+          <t>3584; 10561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4872; 13022</t>
+          <t>4562; 12386</t>
         </is>
       </c>
     </row>
@@ -2702,37 +2702,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6952</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5731</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10231</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7315</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>7078</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>9593</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>15721</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6355</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6952</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5731</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10231</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13909</t>
+          <t>13212</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3772; 10583</t>
+          <t>3758; 10397</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5749; 13862</t>
+          <t>2766; 9557</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11199; 20346</t>
+          <t>5979; 15176</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2966; 9320</t>
+          <t>4507; 9355</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3844; 10482</t>
+          <t>3808; 10620</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2831; 9572</t>
+          <t>5700; 13524</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6236; 15032</t>
+          <t>11001; 20644</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4058; 9686</t>
+          <t>2771; 8672</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9648; 18737</t>
+          <t>9469; 18877</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10009; 21323</t>
+          <t>9914; 20992</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20073; 33174</t>
+          <t>19497; 32509</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9249; 17974</t>
+          <t>8733; 17404</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5912</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2663</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4360</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1311</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>12179</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>2584</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4450</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5912</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2663</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8948</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4186</t>
+          <t>652; 4912</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8878; 15860</t>
+          <t>2820; 8903</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>615; 4827</t>
+          <t>784; 5246</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2395; 6549</t>
+          <t>1882; 7084</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>643; 4900</t>
+          <t>0; 4094</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2920; 8946</t>
+          <t>8190; 15450</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>742; 4866</t>
+          <t>662; 5058</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1728; 7327</t>
+          <t>2537; 6692</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1345; 7474</t>
+          <t>1883; 7538</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13139; 22963</t>
+          <t>13341; 23115</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2544; 8818</t>
+          <t>2615; 8420</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5079; 12122</t>
+          <t>5319; 12406</t>
         </is>
       </c>
     </row>
@@ -3118,37 +3118,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4481</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7843</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4375</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>4857</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>4467</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1475</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4481</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>7843</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7216</t>
+          <t>6385</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2586; 8170</t>
+          <t>1964; 7080</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2120; 7849</t>
+          <t>4393; 11562</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3817</t>
+          <t>0; 3446</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>546; 4426</t>
+          <t>2079; 6779</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1965; 7058</t>
+          <t>2127; 8141</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4239; 11551</t>
+          <t>2126; 7639</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4343</t>
+          <t>0; 3840</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2743; 8238</t>
+          <t>607; 4392</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5830; 13258</t>
+          <t>5874; 13136</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8114; 17386</t>
+          <t>7935; 16948</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>724; 6108</t>
+          <t>702; 5660</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4119; 10677</t>
+          <t>3614; 9444</t>
         </is>
       </c>
     </row>
@@ -3326,37 +3326,37 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>10685</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>6695</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>18123</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>10598</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>13735</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>9978</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>17633</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>10685</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>7204</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>6695</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>19437</t>
+          <t>17666</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>37070</t>
+          <t>35788</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6986; 14732</t>
+          <t>7175; 14860</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9161; 18366</t>
+          <t>3979; 11643</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6323; 13457</t>
+          <t>3976; 9920</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12688; 21726</t>
+          <t>11874; 24825</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6502; 14353</t>
+          <t>7095; 14420</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3900; 11746</t>
+          <t>9342; 18558</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3989; 9514</t>
+          <t>6481; 13345</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>12923; 26309</t>
+          <t>12936; 21939</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16154; 26966</t>
+          <t>15971; 26705</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15197; 27555</t>
+          <t>14894; 27786</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12334; 21490</t>
+          <t>11619; 21025</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28579; 44986</t>
+          <t>26342; 43596</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>18915</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>10407</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>10819</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>6106</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>9017</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>6349</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>12026</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3335</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>18915</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>10407</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>10819</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>9227</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5767; 13450</t>
+          <t>14297; 23671</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3385; 10619</t>
+          <t>6491; 15056</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8010; 16352</t>
+          <t>6887; 14912</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1526; 5560</t>
+          <t>3406; 9054</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13881; 23921</t>
+          <t>5633; 13047</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6516; 14668</t>
+          <t>3313; 10651</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6971; 15071</t>
+          <t>8025; 16522</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3479; 9134</t>
+          <t>1325; 5510</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>22035; 34628</t>
+          <t>22010; 34718</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11564; 22320</t>
+          <t>11528; 23096</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>17054; 29181</t>
+          <t>17390; 29130</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6084; 13275</t>
+          <t>5889; 13278</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>114</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>59343</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>75199</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>54153</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>72542</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>41295</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>78711</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>63172</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>71517</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>59343</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>75199</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>54153</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>80096</t>
+          <t>69644</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>151613</t>
+          <t>142186</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>33713; 51225</t>
+          <t>50277; 68940</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>67251; 90680</t>
+          <t>64263; 86818</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53029; 73357</t>
+          <t>45123; 65094</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>43856; 89860</t>
+          <t>61711; 84667</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>50907; 68801</t>
+          <t>32833; 50167</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>64064; 87054</t>
+          <t>66003; 88793</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44835; 63534</t>
+          <t>54080; 73578</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>67131; 91778</t>
+          <t>60145; 80004</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>89310; 114590</t>
+          <t>89012; 113480</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>138640; 172841</t>
+          <t>137731; 170864</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>103391; 131952</t>
+          <t>104113; 131183</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>113536; 171925</t>
+          <t>128241; 156954</t>
         </is>
       </c>
     </row>
